--- a/Colorado_River_Math.xlsx
+++ b/Colorado_River_Math.xlsx
@@ -75,7 +75,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -107,7 +107,6 @@
         <color rgb="00000000"/>
       </right>
     </border>
-    <border/>
     <border>
       <left style="thin">
         <color rgb="00000000"/>
@@ -144,13 +143,13 @@
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/Colorado_River_Math.xlsx
+++ b/Colorado_River_Math.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>03/04/2026 04:24PM</t>
+          <t>03/05/2026 05:31AM</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,9 @@
       <c r="K28" s="9" t="n">
         <v>9.2049</v>
       </c>
-      <c r="L28" s="10" t="inlineStr"/>
+      <c r="L28" s="10" t="n">
+        <v>7.8931</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
@@ -9011,7 +9013,9 @@
       <c r="K29" s="9" t="n">
         <v>8.952500000000001</v>
       </c>
-      <c r="L29" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="n">
+        <v>8.384399999999999</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
@@ -9059,7 +9063,9 @@
       <c r="K30" s="9" t="n">
         <v>7.8273</v>
       </c>
-      <c r="L30" s="10" t="inlineStr"/>
+      <c r="L30" s="10" t="n">
+        <v>7.9353</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">

--- a/Colorado_River_Math.xlsx
+++ b/Colorado_River_Math.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00;[red]-#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00;[Red]-#,##0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -980,7 +980,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>03/05/2026 05:31AM</t>
+          <t>03/05/2026 09:27AM</t>
         </is>
       </c>
     </row>
